--- a/output/pdf_financials_xlsx/BRM.xlsx
+++ b/output/pdf_financials_xlsx/BRM.xlsx
@@ -2412,19 +2412,19 @@
         <v>6.469023</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.471304</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.775018</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>2.291799</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>5.212852</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>11.504755</v>
       </c>
     </row>
     <row r="35">
@@ -2528,19 +2528,19 @@
         <v>6.469023</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.471304</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.775018</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>2.291799</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>5.212852</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>11.504755</v>
       </c>
     </row>
     <row r="37">
@@ -3224,13 +3224,13 @@
         <v>2.676476</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>15.263767</v>
+        <v>10.792463</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>16.886516</v>
+        <v>13.111498</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>19.703258</v>
+        <v>17.411459</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -45284,7 +45284,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">

--- a/output/pdf_financials_xlsx/BRM.xlsx
+++ b/output/pdf_financials_xlsx/BRM.xlsx
@@ -2061,22 +2061,22 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.545598</v>
+        <v>0.226198</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.556164</v>
+        <v>0.215085</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.5227810000000001</v>
+        <v>0.21357</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.40824</v>
+        <v>0.207768</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.360146</v>
+        <v>0.189021</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.121607</v>
+        <v>0.027057</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.050969</v>
@@ -2119,13 +2119,13 @@
         <v>-0.502838</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.267253</v>
+        <v>-2.586653</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.813252</v>
+        <v>-3.154331</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.307211</v>
+        <v>-0.616422</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.810458</v>
+        <v>1.715908</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0.598244</v>
@@ -2183,13 +2183,13 @@
         <v>-2.663588268765622</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-13.06054717067648</v>
+        <v>-14.90045597940408</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-23.35580287409212</v>
+        <v>-26.1874631336396</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1.992506317160365</v>
+        <v>-3.997984216179195</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.72535216315615</v>
+        <v>10.165227572016</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>3.763453103664247</v>
@@ -6243,22 +6243,22 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.226198</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.215085</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.21357</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.207768</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.189021</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.027057</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>0</v>
@@ -30482,7 +30482,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -31072,7 +31072,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -32959,7 +32959,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BRM.xlsx
+++ b/output/pdf_financials_xlsx/BRM.xlsx
@@ -1275,15 +1275,11 @@
       <c r="F16" s="3" t="n">
         <v>-0.829992</v>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G16" s="3" t="n">
+        <v>0.717625</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-1.72221</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>1.688851</v>
@@ -1295,12 +1291,10 @@
         <v>1.530116</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>4.665763</v>
-      </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.715763</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>-1.026009</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>2.034328</v>
@@ -1355,10 +1349,10 @@
         <v>-0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>2.95</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.276415</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0.736991</v>
@@ -1581,15 +1575,11 @@
       <c r="F20" s="3" t="n">
         <v>-0.829992</v>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="3" t="n">
+        <v>0.717625</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>-1.72221</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.688851</v>
@@ -1603,10 +1593,8 @@
       <c r="L20" s="3" t="n">
         <v>4.665763</v>
       </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M20" s="3" t="n">
+        <v>-1.302424</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>1.297337</v>
@@ -1761,15 +1749,11 @@
       <c r="F23" s="3" t="n">
         <v>-0.829992</v>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G23" s="3" t="n">
+        <v>0.717625</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>-1.72221</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>1.688851</v>
@@ -1783,10 +1767,8 @@
       <c r="L23" s="3" t="n">
         <v>4.665763</v>
       </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M23" s="3" t="n">
+        <v>-1.302424</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>1.297337</v>
@@ -1941,15 +1923,11 @@
       <c r="F26" s="3" t="n">
         <v>11.857029</v>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G26" s="3" t="n">
+        <v>23.920833</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>13.247769</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>28.147517</v>
@@ -1963,10 +1941,8 @@
       <c r="L26" s="3" t="n">
         <v>38.881358</v>
       </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M26" s="3" t="n">
+        <v>43.414133</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>32.433425</v>
@@ -2005,15 +1981,11 @@
       <c r="F27" s="3" t="n">
         <v>-0.829992</v>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G27" s="3" t="n">
+        <v>0.717625</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>-1.72221</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.688851</v>
@@ -2025,12 +1997,10 @@
         <v>1.530116</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>4.665763</v>
-      </c>
-      <c r="M27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.715763</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>-1.026009</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>2.034328</v>
@@ -2127,15 +2097,11 @@
       <c r="F29" s="3" t="n">
         <v>-0.616422</v>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G29" s="3" t="n">
+        <v>0.925393</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>-1.533189</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.715908</v>
@@ -2147,12 +2113,10 @@
         <v>1.56535</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>4.716461</v>
-      </c>
-      <c r="M29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.766461</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>-0.817484</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>2.377952</v>
@@ -2191,15 +2155,11 @@
       <c r="F30" s="3" t="n">
         <v>-3.997984216179195</v>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G30" s="3" t="n">
+        <v>4.722255873496881</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>-14.3514801169918</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10.165227572016</v>
@@ -2211,12 +2171,10 @@
         <v>6.939140279817558</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>19.38311976656062</v>
-      </c>
-      <c r="M30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.259579826051449</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>-3.958930725879676</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>9.714651080315109</v>
@@ -2255,15 +2213,11 @@
       <c r="F31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>0</v>
@@ -2275,12 +2229,10 @@
         <v>0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>171.9351682021351</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>-26.94079681562248</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>36.2277371200711</v>
@@ -2319,15 +2271,11 @@
       <c r="F32" s="3" t="n">
         <v>-5.383154584935324</v>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G32" s="3" t="n">
+        <v>3.662021293891567</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>-16.12081913729126</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>10.00493893042447</v>
@@ -2341,10 +2289,8 @@
       <c r="L32" s="3" t="n">
         <v>19.17476748591522</v>
       </c>
-      <c r="M32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M32" s="3" t="n">
+        <v>-6.307409553854401</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>5.300012905467715</v>
@@ -4550,19 +4496,19 @@
         <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.185687</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.157476</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.175685</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.119561</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.081678</v>
       </c>
     </row>
     <row r="71">
@@ -4608,19 +4554,19 @@
         <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.185687</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.157476</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.175685</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.119561</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.081678</v>
       </c>
     </row>
     <row r="72">
@@ -4840,13 +4786,13 @@
         <v>0.567169</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>2.630554</v>
+        <v>2.444867</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>2.973888</v>
+        <v>2.816412</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>1.318727</v>
+        <v>1.143042</v>
       </c>
       <c r="Q75" s="3" t="n">
         <v>0</v>
@@ -5142,19 +5088,19 @@
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.2392271277075043</v>
+        <v>0.3337575707284343</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.06911521665601532</v>
+        <v>0.1039507777035243</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.1537782830849499</v>
+        <v>0.1799227207418095</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.09495351706899607</v>
+        <v>0.1062062291654569</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.05977441452991682</v>
+        <v>0.06524668988912073</v>
       </c>
     </row>
     <row r="81">
@@ -6187,15 +6133,11 @@
       <c r="F99" s="3" t="n">
         <v>-0.829992</v>
       </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G99" s="3" t="n">
+        <v>0.717625</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>-1.72221</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>1.688851</v>
@@ -6209,10 +6151,8 @@
       <c r="L99" s="3" t="n">
         <v>4.665763</v>
       </c>
-      <c r="M99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M99" s="3" t="n">
+        <v>-1.302424</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>1.297337</v>
@@ -6588,10 +6528,10 @@
         <v>0</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>1.677572</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>1.413096</v>
+        <v>-0.07188600000000001</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-1.339855</v>
@@ -6881,31 +6821,31 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.342308</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.29462</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006012</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.02593</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.029802</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006464</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01196</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014338</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.230718</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -7343,10 +7283,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C119" s="3" t="n">
+        <v>-0.291784</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>-0.342308</v>
@@ -7639,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -7697,7 +7635,7 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -8265,31 +8203,31 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.342308</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.29462</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006012</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.02593</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.029802</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006464</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01196</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014338</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.230718</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -8327,31 +8265,31 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.467108</v>
+        <v>-1.809416</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>1.55764</v>
+        <v>1.26302</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.530207</v>
+        <v>-0.536219</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>0.733706</v>
+        <v>0.707776</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.445593</v>
+        <v>-0.475395</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>2.149387</v>
+        <v>2.142923</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.625181</v>
+        <v>-0.637141</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>1.173251</v>
+        <v>1.158913</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.002526</v>
+        <v>-0.233244</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>2.527635</v>
@@ -8383,7 +8321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U412"/>
+  <dimension ref="A1:U429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9528,7 +9466,11 @@
           <t>Lease liabilities 19</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -12160,7 +12102,11 @@
           <t>Lease liabilities 22</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -23036,7 +22982,11 @@
           <t>Deferred tax expense 6</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -25321,7 +25271,11 @@
           <t>Deferred tax expense 6</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -26610,7 +26564,11 @@
           <t>Deferred tax expense (recovery) 7</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -29407,7 +29365,11 @@
           <t>Purchase of equipment 13</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -33064,7 +33026,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -34784,10 +34750,8 @@
       <c r="F270" s="5" t="n">
         <v>-0.502838</v>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G270" s="5" t="n">
+        <v>-3.137781</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -34883,10 +34847,8 @@
       <c r="F271" s="5" t="n">
         <v>0.218121</v>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G271" s="5" t="n">
+        <v>0.333272</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -34982,10 +34944,8 @@
       <c r="F272" s="5" t="n">
         <v>0.258218</v>
       </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G272" s="5" t="n">
+        <v>0.25241</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -35081,10 +35041,8 @@
       <c r="F273" s="5" t="n">
         <v>0.091768</v>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G273" s="5" t="n">
+        <v>0.143468</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -35180,10 +35138,8 @@
       <c r="F274" s="5" t="n">
         <v>0.119268</v>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G274" s="5" t="n">
+        <v>0.191433</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -35269,22 +35225,18 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Transfer of equipment to cost of goods sold</t>
+          <t>Stock option compensation</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" s="5" t="n">
-        <v>0.052876</v>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.279724</v>
+      </c>
+      <c r="F275" s="5" t="n">
+        <v>0.231202</v>
+      </c>
+      <c r="G275" s="5" t="n">
+        <v>0.181922</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -35370,20 +35322,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Stock option compensation</t>
+          <t>Write down of long term tax asset</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
-      <c r="E276" s="5" t="n">
-        <v>0.279724</v>
-      </c>
-      <c r="F276" s="5" t="n">
-        <v>0.231202</v>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G276" s="5" t="n">
+        <v>0.25</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -35574,20 +35528,24 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Net changes in operating assets and liabilities (note 13)</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" s="5" t="n">
-        <v>-3.13343</v>
+          <t>Net changes in non cash operating working capital (note 12)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F278" s="5" t="n">
         <v>1.677572</v>
       </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G278" s="5" t="n">
+        <v>-0.07188600000000001</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -35668,25 +35626,25 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Investing</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Purchase of plant and equipment</t>
+          <t>Cash provided by (used in) operations</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
-      <c r="E279" s="5" t="n">
-        <v>-0.083123</v>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F279" s="5" t="n">
-        <v>-0.291784</v>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.123311</v>
+      </c>
+      <c r="G279" s="5" t="n">
+        <v>-1.857163</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -35767,31 +35725,23 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Proceeds of long-term debt</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>IssuanceOfDebt</t>
-        </is>
-      </c>
+          <t>Purchase of plant and equipment</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.083123</v>
+      </c>
+      <c r="F280" s="5" t="n">
+        <v>-0.291784</v>
+      </c>
+      <c r="G280" s="5" t="n">
+        <v>-0.342308</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -35872,27 +35822,29 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Financing costs</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
-      <c r="E281" s="5" t="n">
-        <v>-0.320951</v>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F281" s="5" t="n">
+        <v>-0.291784</v>
+      </c>
+      <c r="G281" s="5" t="n">
+        <v>-0.342308</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -35978,22 +35930,26 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Financing total</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" s="5" t="n">
-        <v>2.679049</v>
+          <t>Payment of long-term debt</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G282" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -36079,19 +36035,17 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Financing costs</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
       <c r="E283" s="5" t="n">
-        <v>-0.061848</v>
-      </c>
-      <c r="F283" s="5" t="n">
-        <v>1.831527</v>
+        <v>-0.320951</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -36182,20 +36136,26 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Cash and short-term investments, beginning of year</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" s="5" t="n">
-        <v>2.261135</v>
-      </c>
-      <c r="F284" s="5" t="n">
-        <v>2.199287</v>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash used in financing activities</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G284" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -36281,20 +36241,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Cash and short-term investments, end of year $</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>Increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E285" s="5" t="n">
-        <v>2.199287</v>
+        <v>-0.061848</v>
       </c>
       <c r="F285" s="5" t="n">
-        <v>4.030814</v>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.831527</v>
+      </c>
+      <c r="G285" s="5" t="n">
+        <v>-3.199471</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -36370,107 +36332,125 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Revenue 4</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and short-term investments, beginning of year</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" s="5" t="n">
+        <v>2.261135</v>
+      </c>
+      <c r="F286" s="5" t="n">
+        <v>2.199287</v>
       </c>
       <c r="G286" s="5" t="n">
-        <v>17.359556</v>
-      </c>
-      <c r="H286" s="5" t="n">
-        <v>12.045195</v>
-      </c>
-      <c r="I286" s="5" t="n">
-        <v>15.41832</v>
-      </c>
-      <c r="J286" s="5" t="n">
-        <v>19.596418</v>
-      </c>
-      <c r="K286" s="5" t="n">
-        <v>10.683142</v>
-      </c>
-      <c r="L286" s="5" t="n">
-        <v>16.880173</v>
-      </c>
-      <c r="M286" s="5" t="n">
-        <v>15.896146</v>
-      </c>
-      <c r="N286" s="5" t="n">
-        <v>22.55827</v>
-      </c>
-      <c r="O286" s="5" t="n">
-        <v>24.332827</v>
-      </c>
-      <c r="P286" s="5" t="n">
-        <v>20.649111</v>
-      </c>
-      <c r="Q286" s="5" t="n">
-        <v>24.477997</v>
-      </c>
-      <c r="R286" s="5" t="n">
-        <v>28.862972</v>
-      </c>
-      <c r="S286" s="5" t="n">
-        <v>25.165448</v>
-      </c>
-      <c r="T286" s="5" t="n">
-        <v>37.418959</v>
-      </c>
-      <c r="U286" s="5" t="n">
-        <v>42.35535</v>
+        <v>4.030814</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Cost of goods sold 9,11,16</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and short-term investments, end of year $</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" s="5" t="n">
+        <v>2.199287</v>
+      </c>
+      <c r="F287" s="5" t="n">
+        <v>4.030814</v>
+      </c>
+      <c r="G287" s="5" t="n">
+        <v>0.8313430000000001</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -36527,37 +36507,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S287" s="5" t="n">
-        <v>18.143436</v>
-      </c>
-      <c r="T287" s="5" t="n">
-        <v>27.363044</v>
-      </c>
-      <c r="U287" s="5" t="n">
-        <v>29.588252</v>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Items not involving cash</t>
+        </is>
+      </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Transfer of equipment to cost of goods sold</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" s="5" t="n">
+        <v>0.052876</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -36569,79 +36553,99 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H288" s="5" t="n">
-        <v>2.869289</v>
-      </c>
-      <c r="I288" s="5" t="n">
-        <v>3.495371</v>
-      </c>
-      <c r="J288" s="5" t="n">
-        <v>5.866446</v>
-      </c>
-      <c r="K288" s="5" t="n">
-        <v>2.230642</v>
-      </c>
-      <c r="L288" s="5" t="n">
-        <v>5.995413</v>
-      </c>
-      <c r="M288" s="5" t="n">
-        <v>4.107395</v>
-      </c>
-      <c r="N288" s="5" t="n">
-        <v>6.270412</v>
-      </c>
-      <c r="O288" s="5" t="n">
-        <v>6.377924</v>
-      </c>
-      <c r="P288" s="5" t="n">
-        <v>4.864006</v>
-      </c>
-      <c r="Q288" s="5" t="n">
-        <v>6.236413</v>
-      </c>
-      <c r="R288" s="5" t="n">
-        <v>8.76164</v>
-      </c>
-      <c r="S288" s="5" t="n">
-        <v>7.022012</v>
-      </c>
-      <c r="T288" s="5" t="n">
-        <v>10.055915</v>
-      </c>
-      <c r="U288" s="5" t="n">
-        <v>12.767098</v>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Sales and marketing 16</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>SellingAndMarketingExpense</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net changes in operating assets and liabilities (note 13)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" s="5" t="n">
+        <v>-3.13343</v>
+      </c>
+      <c r="F289" s="5" t="n">
+        <v>1.677572</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -36698,44 +36702,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R289" s="5" t="n">
-        <v>2.583249</v>
-      </c>
-      <c r="S289" s="5" t="n">
-        <v>2.278804</v>
-      </c>
-      <c r="T289" s="5" t="n">
-        <v>3.494411</v>
-      </c>
-      <c r="U289" s="5" t="n">
-        <v>3.527214</v>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Research and development 16</t>
+          <t>Proceeds of long-term debt</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -36797,44 +36807,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R290" s="5" t="n">
-        <v>0.097123</v>
-      </c>
-      <c r="S290" s="5" t="n">
-        <v>0.03044</v>
-      </c>
-      <c r="T290" s="5" t="n">
-        <v>0.043859</v>
-      </c>
-      <c r="U290" s="5" t="n">
-        <v>0.048161</v>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>General and administration 16,19</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Financing total</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" s="5" t="n">
+        <v>2.679049</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -36896,17 +36908,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R291" s="5" t="n">
-        <v>3.202565</v>
-      </c>
-      <c r="S291" s="5" t="n">
-        <v>1.62669</v>
-      </c>
-      <c r="T291" s="5" t="n">
-        <v>2.12389</v>
-      </c>
-      <c r="U291" s="5" t="n">
-        <v>2.616992</v>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="292">
@@ -36915,19 +36935,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Revenue 4</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -36940,74 +36956,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G292" s="5" t="n">
+        <v>17.359556</v>
+      </c>
+      <c r="H292" s="5" t="n">
+        <v>12.045195</v>
+      </c>
+      <c r="I292" s="5" t="n">
+        <v>15.41832</v>
+      </c>
+      <c r="J292" s="5" t="n">
+        <v>19.596418</v>
+      </c>
+      <c r="K292" s="5" t="n">
+        <v>10.683142</v>
+      </c>
+      <c r="L292" s="5" t="n">
+        <v>16.880173</v>
+      </c>
+      <c r="M292" s="5" t="n">
+        <v>15.896146</v>
+      </c>
+      <c r="N292" s="5" t="n">
+        <v>22.55827</v>
+      </c>
+      <c r="O292" s="5" t="n">
+        <v>24.332827</v>
+      </c>
+      <c r="P292" s="5" t="n">
+        <v>20.649111</v>
+      </c>
+      <c r="Q292" s="5" t="n">
+        <v>24.477997</v>
+      </c>
+      <c r="R292" s="5" t="n">
+        <v>28.862972</v>
       </c>
       <c r="S292" s="5" t="n">
-        <v>0.023516</v>
+        <v>25.165448</v>
       </c>
       <c r="T292" s="5" t="n">
-        <v>0.049793</v>
+        <v>37.418959</v>
       </c>
       <c r="U292" s="5" t="n">
-        <v>0.084203</v>
+        <v>42.35535</v>
       </c>
     </row>
     <row r="293">
@@ -37016,19 +37008,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
+          <t>Cost of goods sold 9,11,16</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -37076,29 +37064,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N293" s="5" t="n">
-        <v>4.741872</v>
-      </c>
-      <c r="O293" s="5" t="n">
-        <v>4.657102</v>
-      </c>
-      <c r="P293" s="5" t="n">
-        <v>5.886695</v>
-      </c>
-      <c r="Q293" s="5" t="n">
-        <v>4.166225</v>
-      </c>
-      <c r="R293" s="5" t="n">
-        <v>6.121053</v>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S293" s="5" t="n">
-        <v>3.95945</v>
+        <v>18.143436</v>
       </c>
       <c r="T293" s="5" t="n">
-        <v>5.711953</v>
+        <v>27.363044</v>
       </c>
       <c r="U293" s="5" t="n">
-        <v>6.27657</v>
+        <v>29.588252</v>
       </c>
     </row>
     <row r="294">
@@ -37107,17 +37105,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Earnings from operations</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -37133,61 +37131,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H294" s="5" t="n">
+        <v>2.869289</v>
+      </c>
+      <c r="I294" s="5" t="n">
+        <v>3.495371</v>
+      </c>
+      <c r="J294" s="5" t="n">
+        <v>5.866446</v>
+      </c>
+      <c r="K294" s="5" t="n">
+        <v>2.230642</v>
+      </c>
+      <c r="L294" s="5" t="n">
+        <v>5.995413</v>
+      </c>
+      <c r="M294" s="5" t="n">
+        <v>4.107395</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>1.52854</v>
+        <v>6.270412</v>
       </c>
       <c r="O294" s="5" t="n">
-        <v>1.715763</v>
-      </c>
-      <c r="P294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.377924</v>
+      </c>
+      <c r="P294" s="5" t="n">
+        <v>4.864006</v>
       </c>
       <c r="Q294" s="5" t="n">
-        <v>2.070188</v>
+        <v>6.236413</v>
       </c>
       <c r="R294" s="5" t="n">
-        <v>2.640587</v>
+        <v>8.76164</v>
       </c>
       <c r="S294" s="5" t="n">
-        <v>3.062562</v>
+        <v>7.022012</v>
       </c>
       <c r="T294" s="5" t="n">
-        <v>4.343962</v>
+        <v>10.055915</v>
       </c>
       <c r="U294" s="5" t="n">
-        <v>6.490528</v>
+        <v>12.767098</v>
       </c>
     </row>
     <row r="295">
@@ -37203,10 +37187,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Finance costs 13,19,20</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
+          <t>Sales and marketing 16</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>SellingAndMarketingExpense</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -37272,19 +37260,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R295" s="5" t="n">
+        <v>2.583249</v>
       </c>
       <c r="S295" s="5" t="n">
-        <v>0.273435</v>
+        <v>2.278804</v>
       </c>
       <c r="T295" s="5" t="n">
-        <v>0.195476</v>
+        <v>3.494411</v>
       </c>
       <c r="U295" s="5" t="n">
-        <v>0.161977</v>
+        <v>3.527214</v>
       </c>
     </row>
     <row r="296">
@@ -37300,12 +37286,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Earnings before tax</t>
+          <t>Research and development 16</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -37368,20 +37354,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q296" s="5" t="n">
-        <v>2.034328</v>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R296" s="5" t="n">
-        <v>2.383408</v>
+        <v>0.097123</v>
       </c>
       <c r="S296" s="5" t="n">
-        <v>2.789127</v>
+        <v>0.03044</v>
       </c>
       <c r="T296" s="5" t="n">
-        <v>4.148486</v>
+        <v>0.043859</v>
       </c>
       <c r="U296" s="5" t="n">
-        <v>6.328551</v>
+        <v>0.048161</v>
       </c>
     </row>
     <row r="297">
@@ -37397,12 +37385,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Income tax 6</t>
+          <t>General and administration 16,19</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -37471,16 +37459,16 @@
         </is>
       </c>
       <c r="R297" s="5" t="n">
-        <v>0.770351</v>
+        <v>3.202565</v>
       </c>
       <c r="S297" s="5" t="n">
-        <v>0.609741</v>
+        <v>1.62669</v>
       </c>
       <c r="T297" s="5" t="n">
-        <v>1.104753</v>
+        <v>2.12389</v>
       </c>
       <c r="U297" s="5" t="n">
-        <v>1.511954</v>
+        <v>2.616992</v>
       </c>
     </row>
     <row r="298">
@@ -37496,12 +37484,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Net earnings</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -37549,31 +37537,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N298" s="5" t="n">
-        <v>1.530116</v>
-      </c>
-      <c r="O298" s="5" t="n">
-        <v>4.665763</v>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P298" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q298" s="5" t="n">
-        <v>1.297337</v>
-      </c>
-      <c r="R298" s="5" t="n">
-        <v>1.613057</v>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S298" s="5" t="n">
-        <v>2.179386</v>
+        <v>0.023516</v>
       </c>
       <c r="T298" s="5" t="n">
-        <v>3.043733</v>
+        <v>0.049793</v>
       </c>
       <c r="U298" s="5" t="n">
-        <v>4.816597</v>
+        <v>0.084203</v>
       </c>
     </row>
     <row r="299">
@@ -37589,12 +37585,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Earnings per share, basic 7</t>
+          <t>Total operating expenses</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -37642,37 +37638,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N299" s="5" t="n">
+        <v>4.741872</v>
+      </c>
+      <c r="O299" s="5" t="n">
+        <v>4.657102</v>
+      </c>
+      <c r="P299" s="5" t="n">
+        <v>5.886695</v>
+      </c>
+      <c r="Q299" s="5" t="n">
+        <v>4.166225</v>
       </c>
       <c r="R299" s="5" t="n">
-        <v>1e-07</v>
+        <v>6.121053</v>
       </c>
       <c r="S299" s="5" t="n">
-        <v>1.4e-07</v>
+        <v>3.95945</v>
       </c>
       <c r="T299" s="5" t="n">
-        <v>1.9e-07</v>
+        <v>5.711953</v>
       </c>
       <c r="U299" s="5" t="n">
-        <v>3e-07</v>
+        <v>6.27657</v>
       </c>
     </row>
     <row r="300">
@@ -37688,12 +37676,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Earnings per share, diluted 7</t>
+          <t>Earnings from operations</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -37741,37 +37729,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N300" s="5" t="n">
+        <v>1.52854</v>
+      </c>
+      <c r="O300" s="5" t="n">
+        <v>1.715763</v>
       </c>
       <c r="P300" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q300" s="5" t="n">
+        <v>2.070188</v>
       </c>
       <c r="R300" s="5" t="n">
-        <v>9e-08</v>
+        <v>2.640587</v>
       </c>
       <c r="S300" s="5" t="n">
-        <v>1.3e-07</v>
+        <v>3.062562</v>
       </c>
       <c r="T300" s="5" t="n">
-        <v>1.6e-07</v>
+        <v>4.343962</v>
       </c>
       <c r="U300" s="5" t="n">
-        <v>2.6e-07</v>
+        <v>6.490528</v>
       </c>
     </row>
     <row r="301">
@@ -37782,12 +37764,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Item that will be reclassified into earnings</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences on foreign operations</t>
+          <t>Finance costs 13,19,20</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -37856,17 +37838,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R301" s="5" t="n">
-        <v>0.849494</v>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S301" s="5" t="n">
-        <v>-0.176804</v>
+        <v>0.273435</v>
       </c>
       <c r="T301" s="5" t="n">
-        <v>0.561595</v>
+        <v>0.195476</v>
       </c>
       <c r="U301" s="5" t="n">
-        <v>-0.427517</v>
+        <v>0.161977</v>
       </c>
     </row>
     <row r="302">
@@ -37877,15 +37861,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Item that will be reclassified into earnings</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Total comprehensive earnings</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>Earnings before tax</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -37946,22 +37934,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q302" s="5" t="n">
+        <v>2.034328</v>
       </c>
       <c r="R302" s="5" t="n">
-        <v>2.462551</v>
+        <v>2.383408</v>
       </c>
       <c r="S302" s="5" t="n">
-        <v>2.002582</v>
+        <v>2.789127</v>
       </c>
       <c r="T302" s="5" t="n">
-        <v>3.605328</v>
+        <v>4.148486</v>
       </c>
       <c r="U302" s="5" t="n">
-        <v>4.38908</v>
+        <v>6.328551</v>
       </c>
     </row>
     <row r="303">
@@ -37970,15 +37956,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Cost of goods sold 11,16</t>
+          <t>Income tax 6</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -38047,20 +38037,16 @@
         </is>
       </c>
       <c r="R303" s="5" t="n">
-        <v>20.101332</v>
+        <v>0.770351</v>
       </c>
       <c r="S303" s="5" t="n">
-        <v>18.143436</v>
-      </c>
-      <c r="T303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.609741</v>
+      </c>
+      <c r="T303" s="5" t="n">
+        <v>1.104753</v>
+      </c>
+      <c r="U303" s="5" t="n">
+        <v>1.511954</v>
       </c>
     </row>
     <row r="304">
@@ -38076,12 +38062,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Other expense</t>
+          <t>Net earnings</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -38129,41 +38115,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N304" s="5" t="n">
+        <v>1.530116</v>
+      </c>
+      <c r="O304" s="5" t="n">
+        <v>4.665763</v>
       </c>
       <c r="P304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q304" s="5" t="n">
+        <v>1.297337</v>
       </c>
       <c r="R304" s="5" t="n">
-        <v>0.238116</v>
+        <v>1.613057</v>
       </c>
       <c r="S304" s="5" t="n">
-        <v>0.023516</v>
-      </c>
-      <c r="T304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.179386</v>
+      </c>
+      <c r="T304" s="5" t="n">
+        <v>3.043733</v>
+      </c>
+      <c r="U304" s="5" t="n">
+        <v>4.816597</v>
       </c>
     </row>
     <row r="305">
@@ -38179,10 +38155,14 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Finance costs 13,20</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>Earnings per share, basic 7</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -38249,20 +38229,16 @@
         </is>
       </c>
       <c r="R305" s="5" t="n">
-        <v>0.257179</v>
+        <v>1e-07</v>
       </c>
       <c r="S305" s="5" t="n">
-        <v>0.273435</v>
-      </c>
-      <c r="T305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.4e-07</v>
+      </c>
+      <c r="T305" s="5" t="n">
+        <v>1.9e-07</v>
+      </c>
+      <c r="U305" s="5" t="n">
+        <v>3e-07</v>
       </c>
     </row>
     <row r="306">
@@ -38271,15 +38247,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Cost of goods sold 11,19</t>
+          <t>Earnings per share, diluted 7</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -38342,26 +38322,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q306" s="5" t="n">
-        <v>18.241584</v>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R306" s="5" t="n">
-        <v>20.101332</v>
-      </c>
-      <c r="S306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9e-08</v>
+      </c>
+      <c r="S306" s="5" t="n">
+        <v>1.3e-07</v>
+      </c>
+      <c r="T306" s="5" t="n">
+        <v>1.6e-07</v>
+      </c>
+      <c r="U306" s="5" t="n">
+        <v>2.6e-07</v>
       </c>
     </row>
     <row r="307">
@@ -38372,19 +38348,15 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Item that will be reclassified into earnings</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Sales and marketing 19</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>SellingAndMarketingExpense</t>
-        </is>
-      </c>
+          <t>Foreign currency translation differences on foreign operations</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -38445,26 +38417,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q307" s="5" t="n">
-        <v>2.097576</v>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R307" s="5" t="n">
-        <v>2.583249</v>
-      </c>
-      <c r="S307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.849494</v>
+      </c>
+      <c r="S307" s="5" t="n">
+        <v>-0.176804</v>
+      </c>
+      <c r="T307" s="5" t="n">
+        <v>0.561595</v>
+      </c>
+      <c r="U307" s="5" t="n">
+        <v>-0.427517</v>
       </c>
     </row>
     <row r="308">
@@ -38475,19 +38443,15 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Item that will be reclassified into earnings</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Research and development 19</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
+          <t>Total comprehensive earnings</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -38548,26 +38512,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q308" s="5" t="n">
-        <v>0.014223</v>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R308" s="5" t="n">
-        <v>0.097123</v>
-      </c>
-      <c r="S308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.462551</v>
+      </c>
+      <c r="S308" s="5" t="n">
+        <v>2.002582</v>
+      </c>
+      <c r="T308" s="5" t="n">
+        <v>3.605328</v>
+      </c>
+      <c r="U308" s="5" t="n">
+        <v>4.38908</v>
       </c>
     </row>
     <row r="309">
@@ -38576,19 +38536,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
         <is>
-          <t>General and administration 19,21</t>
+          <t>Cost of goods sold 11,16</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -38651,16 +38607,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q309" s="5" t="n">
-        <v>1.815749</v>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R309" s="5" t="n">
-        <v>3.202565</v>
-      </c>
-      <c r="S309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20.101332</v>
+      </c>
+      <c r="S309" s="5" t="n">
+        <v>18.143436</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -38686,7 +38642,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Other expense 6</t>
+          <t>Other expense</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -38754,16 +38710,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q310" s="5" t="n">
-        <v>0.238677</v>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R310" s="5" t="n">
         <v>0.238116</v>
       </c>
-      <c r="S310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S310" s="5" t="n">
+        <v>0.023516</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -38789,7 +38745,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Finance costs 16,22</t>
+          <t>Finance costs 13,20</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -38853,16 +38809,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q311" s="5" t="n">
-        <v>0.03586</v>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R311" s="5" t="n">
         <v>0.257179</v>
       </c>
-      <c r="S311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S311" s="5" t="n">
+        <v>0.273435</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -38881,19 +38837,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Income tax 7</t>
+          <t>Cost of goods sold 11,19</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -38957,10 +38909,10 @@
         </is>
       </c>
       <c r="Q312" s="5" t="n">
-        <v>0.736991</v>
+        <v>18.241584</v>
       </c>
       <c r="R312" s="5" t="n">
-        <v>0.770351</v>
+        <v>20.101332</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -38991,12 +38943,12 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Earnings per share, basic 8</t>
+          <t>Sales and marketing 19</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingAndMarketingExpense</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -39060,10 +39012,10 @@
         </is>
       </c>
       <c r="Q313" s="5" t="n">
-        <v>4e-08</v>
+        <v>2.097576</v>
       </c>
       <c r="R313" s="5" t="n">
-        <v>1e-07</v>
+        <v>2.583249</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
@@ -39094,12 +39046,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Earnings per share, diluted 8</t>
+          <t>Research and development 19</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -39163,10 +39115,10 @@
         </is>
       </c>
       <c r="Q314" s="5" t="n">
-        <v>4e-08</v>
+        <v>0.014223</v>
       </c>
       <c r="R314" s="5" t="n">
-        <v>9e-08</v>
+        <v>0.097123</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
@@ -39192,15 +39144,19 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Item that will be not reclassified into profit</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences on foreign operations</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>General and administration 19,21</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -39262,10 +39218,10 @@
         </is>
       </c>
       <c r="Q315" s="5" t="n">
-        <v>-0.539547</v>
+        <v>1.815749</v>
       </c>
       <c r="R315" s="5" t="n">
-        <v>0.849494</v>
+        <v>3.202565</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -39291,15 +39247,19 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Item that will be not reclassified into profit</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Total comprehensive earnings</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>Other expense 6</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -39361,10 +39321,10 @@
         </is>
       </c>
       <c r="Q316" s="5" t="n">
-        <v>0.75779</v>
+        <v>0.238677</v>
       </c>
       <c r="R316" s="5" t="n">
-        <v>2.462551</v>
+        <v>0.238116</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
@@ -39388,17 +39348,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Cost of goods sold 11</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Finance costs 16,22</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -39449,21 +39409,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O317" s="5" t="n">
-        <v>17.954903</v>
-      </c>
-      <c r="P317" s="5" t="n">
-        <v>15.785105</v>
-      </c>
-      <c r="Q317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q317" s="5" t="n">
+        <v>0.03586</v>
+      </c>
+      <c r="R317" s="5" t="n">
+        <v>0.257179</v>
       </c>
       <c r="S317" t="inlineStr">
         <is>
@@ -39494,12 +39454,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Sales and marketing</t>
+          <t>Income tax 7</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>SellingAndMarketingExpense</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -39547,24 +39507,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N318" s="5" t="n">
-        <v>2.164868</v>
-      </c>
-      <c r="O318" s="5" t="n">
-        <v>2.059801</v>
-      </c>
-      <c r="P318" s="5" t="n">
-        <v>2.032653</v>
-      </c>
-      <c r="Q318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q318" s="5" t="n">
+        <v>0.736991</v>
+      </c>
+      <c r="R318" s="5" t="n">
+        <v>0.770351</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
@@ -39595,12 +39557,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Research and development</t>
+          <t>Earnings per share, basic 8</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>ResearchAndDevelopment</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -39648,24 +39610,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N319" s="5" t="n">
-        <v>0.393974</v>
-      </c>
-      <c r="O319" s="5" t="n">
-        <v>0.271523</v>
-      </c>
-      <c r="P319" s="5" t="n">
-        <v>0.046527</v>
-      </c>
-      <c r="Q319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q319" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="R319" s="5" t="n">
+        <v>1e-07</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
@@ -39696,12 +39660,12 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>General and administration</t>
+          <t>Earnings per share, diluted 8</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -39749,24 +39713,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N320" s="5" t="n">
-        <v>2.141004</v>
-      </c>
-      <c r="O320" s="5" t="n">
-        <v>2.852117</v>
-      </c>
-      <c r="P320" s="5" t="n">
-        <v>4.101434</v>
-      </c>
-      <c r="Q320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q320" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="R320" s="5" t="n">
+        <v>9e-08</v>
       </c>
       <c r="S320" t="inlineStr">
         <is>
@@ -39792,19 +39758,15 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Item that will be not reclassified into profit</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Other income 6</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Foreign currency translation differences on foreign operations</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -39855,21 +39817,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O321" s="5" t="n">
-        <v>-0.526339</v>
-      </c>
-      <c r="P321" s="5" t="n">
-        <v>-0.293919</v>
-      </c>
-      <c r="Q321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q321" s="5" t="n">
+        <v>-0.539547</v>
+      </c>
+      <c r="R321" s="5" t="n">
+        <v>0.849494</v>
       </c>
       <c r="S321" t="inlineStr">
         <is>
@@ -39895,19 +39857,15 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Item that will be not reclassified into profit</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Earnings (loss) from operations</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Total comprehensive earnings</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -39958,21 +39916,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O322" s="5" t="n">
-        <v>1.720822</v>
-      </c>
-      <c r="P322" s="5" t="n">
-        <v>-1.022689</v>
-      </c>
-      <c r="Q322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R322" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q322" s="5" t="n">
+        <v>0.75779</v>
+      </c>
+      <c r="R322" s="5" t="n">
+        <v>2.462551</v>
       </c>
       <c r="S322" t="inlineStr">
         <is>
@@ -39996,17 +39954,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B323" t="inlineStr"/>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Finance costs 19</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr"/>
+          <t>Cost of goods sold 11</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -40058,10 +40016,10 @@
         </is>
       </c>
       <c r="O323" s="5" t="n">
-        <v>0.005059</v>
+        <v>17.954903</v>
       </c>
       <c r="P323" s="5" t="n">
-        <v>0.00332</v>
+        <v>15.785105</v>
       </c>
       <c r="Q323" t="inlineStr">
         <is>
@@ -40102,10 +40060,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Earnings (loss) before tax</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
+          <t>Sales and marketing</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>SellingAndMarketingExpense</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -40151,16 +40113,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N324" s="5" t="n">
+        <v>2.164868</v>
       </c>
       <c r="O324" s="5" t="n">
-        <v>1.715763</v>
+        <v>2.059801</v>
       </c>
       <c r="P324" s="5" t="n">
-        <v>-1.026009</v>
+        <v>2.032653</v>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
@@ -40201,10 +40161,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Income tax (recovery) 7</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr"/>
+          <t>Research and development</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -40250,16 +40214,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N325" s="5" t="n">
+        <v>0.393974</v>
       </c>
       <c r="O325" s="5" t="n">
-        <v>-2.95</v>
+        <v>0.271523</v>
       </c>
       <c r="P325" s="5" t="n">
-        <v>0.276415</v>
+        <v>0.046527</v>
       </c>
       <c r="Q325" t="inlineStr">
         <is>
@@ -40300,10 +40262,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Net earnings (loss)</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>General and administration</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -40349,16 +40315,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N326" s="5" t="n">
+        <v>2.141004</v>
       </c>
       <c r="O326" s="5" t="n">
-        <v>4.665763</v>
+        <v>2.852117</v>
       </c>
       <c r="P326" s="5" t="n">
-        <v>-1.302424</v>
+        <v>4.101434</v>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
@@ -40399,12 +40363,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Earnings (loss) per share, basic 8 $</t>
+          <t>Other income 6</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -40458,10 +40422,10 @@
         </is>
       </c>
       <c r="O327" s="5" t="n">
-        <v>1.2e-07</v>
+        <v>-0.526339</v>
       </c>
       <c r="P327" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.293919</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
@@ -40502,12 +40466,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Earnings (loss) per share, diluted 8 $</t>
+          <t>Earnings (loss) from operations</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -40561,10 +40525,10 @@
         </is>
       </c>
       <c r="O328" s="5" t="n">
-        <v>1.2e-07</v>
+        <v>1.720822</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-1.022689</v>
       </c>
       <c r="Q328" t="inlineStr">
         <is>
@@ -40600,12 +40564,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Other comprehensive earnings</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences on foreign operations</t>
+          <t>Finance costs 19</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -40654,14 +40618,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N329" s="5" t="n">
-        <v>0.395665</v>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O329" s="5" t="n">
-        <v>0.821779</v>
+        <v>0.005059</v>
       </c>
       <c r="P329" s="5" t="n">
-        <v>0.040588</v>
+        <v>0.00332</v>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
@@ -40697,12 +40663,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Other comprehensive earnings</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Total comprehensive earnings (loss)</t>
+          <t>Earnings (loss) before tax</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -40757,10 +40723,10 @@
         </is>
       </c>
       <c r="O330" s="5" t="n">
-        <v>5.487542</v>
+        <v>1.715763</v>
       </c>
       <c r="P330" s="5" t="n">
-        <v>-1.261836</v>
+        <v>-1.026009</v>
       </c>
       <c r="Q330" t="inlineStr">
         <is>
@@ -40794,15 +40760,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr"/>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Cost of goods sold 12</t>
+          <t>Income tax (recovery) 7</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -40820,34 +40790,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H331" s="5" t="n">
-        <v>9.175905999999999</v>
-      </c>
-      <c r="I331" s="5" t="n">
-        <v>11.691949</v>
-      </c>
-      <c r="J331" s="5" t="n">
-        <v>13.729972</v>
-      </c>
-      <c r="K331" s="5" t="n">
-        <v>8.452500000000001</v>
-      </c>
-      <c r="L331" s="5" t="n">
-        <v>10.88476</v>
-      </c>
-      <c r="M331" s="5" t="n">
-        <v>11.788751</v>
-      </c>
-      <c r="N331" s="5" t="n">
-        <v>16.287858</v>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O331" s="5" t="n">
-        <v>17.954903</v>
-      </c>
-      <c r="P331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.95</v>
+      </c>
+      <c r="P331" s="5" t="n">
+        <v>0.276415</v>
       </c>
       <c r="Q331" t="inlineStr">
         <is>
@@ -40888,10 +40870,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Other expense (income) 6</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>Net earnings (loss)</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -40937,16 +40923,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N332" s="5" t="n">
-        <v>0.042026</v>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O332" s="5" t="n">
-        <v>-0.526339</v>
-      </c>
-      <c r="P332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.665763</v>
+      </c>
+      <c r="P332" s="5" t="n">
+        <v>-1.302424</v>
       </c>
       <c r="Q332" t="inlineStr">
         <is>
@@ -40987,10 +40973,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Finance costs 7</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>Earnings (loss) per share, basic 8 $</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -41036,18 +41026,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N333" s="5" t="n">
-        <v>-0.001576</v>
-      </c>
-      <c r="O333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O333" s="5" t="n">
+        <v>1.2e-07</v>
+      </c>
+      <c r="P333" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -41088,10 +41076,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Net earnings before tax</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>Earnings (loss) per share, diluted 8 $</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -41137,16 +41129,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N334" s="5" t="n">
-        <v>1.530116</v>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O334" s="5" t="n">
-        <v>1.715763</v>
-      </c>
-      <c r="P334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.2e-07</v>
+      </c>
+      <c r="P334" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -41182,12 +41174,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive earnings</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Income tax recovery 8</t>
+          <t>Foreign currency translation differences on foreign operations</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -41236,18 +41228,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N335" s="5" t="n">
+        <v>0.395665</v>
       </c>
       <c r="O335" s="5" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="P335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.821779</v>
+      </c>
+      <c r="P335" s="5" t="n">
+        <v>0.040588</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -41283,19 +41271,15 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive earnings</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Earnings per share, basic 9 $</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Total comprehensive earnings (loss)</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -41341,16 +41325,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N336" s="5" t="n">
-        <v>4e-08</v>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O336" s="5" t="n">
-        <v>1.2e-07</v>
-      </c>
-      <c r="P336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.487542</v>
+      </c>
+      <c r="P336" s="5" t="n">
+        <v>-1.261836</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -41384,19 +41368,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B337" t="inlineStr"/>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Earnings per share, diluted 9 $</t>
+          <t>Cost of goods sold 12</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -41414,41 +41394,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H337" s="5" t="n">
+        <v>9.175905999999999</v>
+      </c>
+      <c r="I337" s="5" t="n">
+        <v>11.691949</v>
+      </c>
+      <c r="J337" s="5" t="n">
+        <v>13.729972</v>
+      </c>
+      <c r="K337" s="5" t="n">
+        <v>8.452500000000001</v>
+      </c>
+      <c r="L337" s="5" t="n">
+        <v>10.88476</v>
+      </c>
+      <c r="M337" s="5" t="n">
+        <v>11.788751</v>
       </c>
       <c r="N337" s="5" t="n">
-        <v>4e-08</v>
+        <v>16.287858</v>
       </c>
       <c r="O337" s="5" t="n">
-        <v>1.2e-07</v>
+        <v>17.954903</v>
       </c>
       <c r="P337" t="inlineStr">
         <is>
@@ -41489,12 +41457,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Other comprehensive earnings</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Total comprehensive earnings</t>
+          <t>Other expense (income) 6</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
@@ -41544,10 +41512,10 @@
         </is>
       </c>
       <c r="N338" s="5" t="n">
-        <v>1.925781</v>
+        <v>0.042026</v>
       </c>
       <c r="O338" s="5" t="n">
-        <v>5.487542</v>
+        <v>-0.526339</v>
       </c>
       <c r="P338" t="inlineStr">
         <is>
@@ -41588,48 +41556,62 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Sales and marketing</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>SellingAndMarketingExpense</t>
-        </is>
-      </c>
-      <c r="E339" s="5" t="n">
-        <v>3.323177</v>
-      </c>
-      <c r="F339" s="5" t="n">
-        <v>3.62006</v>
-      </c>
-      <c r="G339" s="5" t="n">
-        <v>3.56086</v>
-      </c>
-      <c r="H339" s="5" t="n">
-        <v>2.616715</v>
-      </c>
-      <c r="I339" s="5" t="n">
-        <v>1.602116</v>
-      </c>
-      <c r="J339" s="5" t="n">
-        <v>1.845874</v>
-      </c>
-      <c r="K339" s="5" t="n">
-        <v>1.551085</v>
-      </c>
-      <c r="L339" s="5" t="n">
-        <v>1.90717</v>
-      </c>
-      <c r="M339" s="5" t="n">
-        <v>1.882514</v>
+          <t>Finance costs 7</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N339" s="5" t="n">
-        <v>2.164868</v>
+        <v>-0.001576</v>
       </c>
       <c r="O339" t="inlineStr">
         <is>
@@ -41675,19 +41657,15 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Research and development</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
+          <t>Net earnings before tax</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -41713,25 +41691,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J340" s="5" t="n">
-        <v>0.586561</v>
-      </c>
-      <c r="K340" s="5" t="n">
-        <v>0.547995</v>
-      </c>
-      <c r="L340" s="5" t="n">
-        <v>0.444357</v>
-      </c>
-      <c r="M340" s="5" t="n">
-        <v>0.387278</v>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N340" s="5" t="n">
-        <v>0.393974</v>
-      </c>
-      <c r="O340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.530116</v>
+      </c>
+      <c r="O340" s="5" t="n">
+        <v>1.715763</v>
       </c>
       <c r="P340" t="inlineStr">
         <is>
@@ -41772,53 +41756,71 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>General and administration</t>
+          <t>Income tax recovery 8</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E341" s="5" t="n">
-        <v>1.878411</v>
-      </c>
-      <c r="F341" s="5" t="n">
-        <v>2.153917</v>
-      </c>
-      <c r="G341" s="5" t="n">
-        <v>2.758254</v>
-      </c>
-      <c r="H341" s="5" t="n">
-        <v>2.847635</v>
-      </c>
-      <c r="I341" s="5" t="n">
-        <v>2.002684</v>
-      </c>
-      <c r="J341" s="5" t="n">
-        <v>2.196472</v>
-      </c>
-      <c r="K341" s="5" t="n">
-        <v>1.691773</v>
-      </c>
-      <c r="L341" s="5" t="n">
-        <v>1.798044</v>
-      </c>
-      <c r="M341" s="5" t="n">
-        <v>1.369725</v>
-      </c>
-      <c r="N341" s="5" t="n">
-        <v>2.141004</v>
-      </c>
-      <c r="O341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O341" s="5" t="n">
+        <v>-2.95</v>
       </c>
       <c r="P341" t="inlineStr">
         <is>
@@ -41859,15 +41861,19 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Other expense (income) 6</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>Earnings per share, basic 9 $</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -41908,16 +41914,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M342" s="5" t="n">
-        <v>-0.357047</v>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N342" s="5" t="n">
-        <v>0.042026</v>
-      </c>
-      <c r="O342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4e-08</v>
+      </c>
+      <c r="O342" s="5" t="n">
+        <v>1.2e-07</v>
       </c>
       <c r="P342" t="inlineStr">
         <is>
@@ -41958,53 +41964,69 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
+          <t>Earnings per share, diluted 9 $</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E343" s="5" t="n">
-        <v>6.055764</v>
-      </c>
-      <c r="F343" s="5" t="n">
-        <v>6.201322</v>
-      </c>
-      <c r="G343" s="5" t="n">
-        <v>7.131747</v>
-      </c>
-      <c r="H343" s="5" t="n">
-        <v>5.736097</v>
-      </c>
-      <c r="I343" s="5" t="n">
-        <v>3.867969</v>
-      </c>
-      <c r="J343" s="5" t="n">
-        <v>4.561832</v>
-      </c>
-      <c r="K343" s="5" t="n">
-        <v>3.376591</v>
-      </c>
-      <c r="L343" s="5" t="n">
-        <v>3.797369</v>
-      </c>
-      <c r="M343" s="5" t="n">
-        <v>3.28247</v>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N343" s="5" t="n">
-        <v>4.741872</v>
-      </c>
-      <c r="O343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4e-08</v>
+      </c>
+      <c r="O343" s="5" t="n">
+        <v>1.2e-07</v>
       </c>
       <c r="P343" t="inlineStr">
         <is>
@@ -42045,12 +42067,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Other comprehensive earnings</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Earnings from operations</t>
+          <t>Total comprehensive earnings</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -42089,19 +42111,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L344" s="5" t="n">
-        <v>2.198044</v>
-      </c>
-      <c r="M344" s="5" t="n">
-        <v>0.824925</v>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N344" s="5" t="n">
-        <v>1.52854</v>
-      </c>
-      <c r="O344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.925781</v>
+      </c>
+      <c r="O344" s="5" t="n">
+        <v>5.487542</v>
       </c>
       <c r="P344" t="inlineStr">
         <is>
@@ -42147,45 +42171,43 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Finance costs 7</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Sales and marketing</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>SellingAndMarketingExpense</t>
+        </is>
+      </c>
+      <c r="E345" s="5" t="n">
+        <v>3.323177</v>
+      </c>
+      <c r="F345" s="5" t="n">
+        <v>3.62006</v>
+      </c>
+      <c r="G345" s="5" t="n">
+        <v>3.56086</v>
       </c>
       <c r="H345" s="5" t="n">
-        <v>0.345549</v>
+        <v>2.616715</v>
       </c>
       <c r="I345" s="5" t="n">
-        <v>0.457394</v>
+        <v>1.602116</v>
       </c>
       <c r="J345" s="5" t="n">
-        <v>0.586989</v>
+        <v>1.845874</v>
       </c>
       <c r="K345" s="5" t="n">
-        <v>0.576261</v>
+        <v>1.551085</v>
       </c>
       <c r="L345" s="5" t="n">
-        <v>0.509193</v>
+        <v>1.90717</v>
       </c>
       <c r="M345" s="5" t="n">
-        <v>0.27765</v>
+        <v>1.882514</v>
       </c>
       <c r="N345" s="5" t="n">
-        <v>-0.001576</v>
+        <v>2.164868</v>
       </c>
       <c r="O345" t="inlineStr">
         <is>
@@ -42236,12 +42258,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Net earnings</t>
+          <t>Research and development</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -42269,24 +42291,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J346" s="5" t="n">
+        <v>0.586561</v>
+      </c>
+      <c r="K346" s="5" t="n">
+        <v>0.547995</v>
       </c>
       <c r="L346" s="5" t="n">
-        <v>1.688851</v>
+        <v>0.444357</v>
       </c>
       <c r="M346" s="5" t="n">
-        <v>0.547275</v>
+        <v>0.387278</v>
       </c>
       <c r="N346" s="5" t="n">
-        <v>1.530116</v>
+        <v>0.393974</v>
       </c>
       <c r="O346" t="inlineStr">
         <is>
@@ -42337,57 +42355,43 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Earnings per share, basic 9 $</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="n">
+        <v>1.878411</v>
+      </c>
+      <c r="F347" s="5" t="n">
+        <v>2.153917</v>
+      </c>
+      <c r="G347" s="5" t="n">
+        <v>2.758254</v>
+      </c>
+      <c r="H347" s="5" t="n">
+        <v>2.847635</v>
+      </c>
+      <c r="I347" s="5" t="n">
+        <v>2.002684</v>
+      </c>
+      <c r="J347" s="5" t="n">
+        <v>2.196472</v>
+      </c>
+      <c r="K347" s="5" t="n">
+        <v>1.691773</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>1.3e-07</v>
+        <v>1.798044</v>
       </c>
       <c r="M347" s="5" t="n">
-        <v>4e-08</v>
+        <v>1.369725</v>
       </c>
       <c r="N347" s="5" t="n">
-        <v>4e-08</v>
+        <v>2.141004</v>
       </c>
       <c r="O347" t="inlineStr">
         <is>
@@ -42438,14 +42442,10 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Earnings per share, diluted 9 $</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Other expense (income) 6</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -42481,14 +42481,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L348" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M348" s="5" t="n">
-        <v>2e-08</v>
+        <v>-0.357047</v>
       </c>
       <c r="N348" s="5" t="n">
-        <v>4e-08</v>
+        <v>0.042026</v>
       </c>
       <c r="O348" t="inlineStr">
         <is>
@@ -42534,52 +42536,48 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Other comprehensive earnings (loss)</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences on foreign operations</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr"/>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="n">
+        <v>6.055764</v>
+      </c>
+      <c r="F349" s="5" t="n">
+        <v>6.201322</v>
+      </c>
+      <c r="G349" s="5" t="n">
+        <v>7.131747</v>
+      </c>
+      <c r="H349" s="5" t="n">
+        <v>5.736097</v>
       </c>
       <c r="I349" s="5" t="n">
-        <v>-0.055098</v>
+        <v>3.867969</v>
       </c>
       <c r="J349" s="5" t="n">
-        <v>0.074965</v>
+        <v>4.561832</v>
       </c>
       <c r="K349" s="5" t="n">
-        <v>0.203225</v>
+        <v>3.376591</v>
       </c>
       <c r="L349" s="5" t="n">
-        <v>0.146582</v>
+        <v>3.797369</v>
       </c>
       <c r="M349" s="5" t="n">
-        <v>-0.120286</v>
+        <v>3.28247</v>
       </c>
       <c r="N349" s="5" t="n">
-        <v>0.395665</v>
+        <v>4.741872</v>
       </c>
       <c r="O349" t="inlineStr">
         <is>
@@ -42625,15 +42623,19 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Other comprehensive earnings (loss)</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Total comprehensive earnings</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr"/>
+          <t>Earnings from operations</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -42670,13 +42672,13 @@
         </is>
       </c>
       <c r="L350" s="5" t="n">
-        <v>1.835433</v>
+        <v>2.198044</v>
       </c>
       <c r="M350" s="5" t="n">
-        <v>0.426989</v>
+        <v>0.824925</v>
       </c>
       <c r="N350" s="5" t="n">
-        <v>1.925781</v>
+        <v>1.52854</v>
       </c>
       <c r="O350" t="inlineStr">
         <is>
@@ -42722,12 +42724,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>7.  Finance costs</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Short term interest</t>
+          <t>Finance costs 7</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -42746,29 +42748,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H351" s="5" t="n">
+        <v>0.345549</v>
+      </c>
+      <c r="I351" s="5" t="n">
+        <v>0.457394</v>
+      </c>
+      <c r="J351" s="5" t="n">
+        <v>0.586989</v>
       </c>
       <c r="K351" s="5" t="n">
-        <v>0.007820000000000001</v>
+        <v>0.576261</v>
       </c>
       <c r="L351" s="5" t="n">
-        <v>0.00188</v>
+        <v>0.509193</v>
       </c>
       <c r="M351" s="5" t="n">
-        <v>-0.010292</v>
+        <v>0.27765</v>
       </c>
       <c r="N351" s="5" t="n">
         <v>-0.001576</v>
@@ -42817,15 +42813,19 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>7.  Finance costs</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Long-term debt interest</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr"/>
+          <t>Net earnings</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -42856,19 +42856,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K352" s="5" t="n">
-        <v>0.568441</v>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L352" s="5" t="n">
-        <v>0.507313</v>
+        <v>1.688851</v>
       </c>
       <c r="M352" s="5" t="n">
-        <v>0.287942</v>
-      </c>
-      <c r="N352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.547275</v>
+      </c>
+      <c r="N352" s="5" t="n">
+        <v>1.530116</v>
       </c>
       <c r="O352" t="inlineStr">
         <is>
@@ -42914,15 +42914,19 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>7.  Finance costs</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>7.  Finance costs total</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr"/>
+          <t>Earnings per share, basic 9 $</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -42953,17 +42957,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K353" s="5" t="n">
-        <v>0.576261</v>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L353" s="5" t="n">
-        <v>0.509193</v>
+        <v>1.3e-07</v>
       </c>
       <c r="M353" s="5" t="n">
-        <v>0.27765</v>
+        <v>4e-08</v>
       </c>
       <c r="N353" s="5" t="n">
-        <v>-0.001576</v>
+        <v>4e-08</v>
       </c>
       <c r="O353" t="inlineStr">
         <is>
@@ -43014,12 +43020,12 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Other income 6</t>
+          <t>Earnings per share, diluted 9 $</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -43032,31 +43038,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G354" s="5" t="n">
-        <v>-1.079618</v>
-      </c>
-      <c r="H354" s="5" t="n">
-        <v>-0.799905</v>
-      </c>
-      <c r="I354" s="5" t="n">
-        <v>-0.276387</v>
-      </c>
-      <c r="J354" s="5" t="n">
-        <v>-0.067075</v>
-      </c>
-      <c r="K354" s="5" t="n">
-        <v>-0.414262</v>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L354" s="5" t="n">
-        <v>-0.352202</v>
+        <v>5.999999999999999e-08</v>
       </c>
       <c r="M354" s="5" t="n">
-        <v>-0.357047</v>
-      </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2e-08</v>
+      </c>
+      <c r="N354" s="5" t="n">
+        <v>4e-08</v>
       </c>
       <c r="O354" t="inlineStr">
         <is>
@@ -43102,19 +43116,15 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Other comprehensive earnings (loss)</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Earnings (loss) from operations</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Foreign currency translation differences on foreign operations</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -43136,26 +43146,22 @@
         </is>
       </c>
       <c r="I355" s="5" t="n">
-        <v>-0.372598</v>
+        <v>-0.055098</v>
       </c>
       <c r="J355" s="5" t="n">
-        <v>1.304614</v>
+        <v>0.074965</v>
       </c>
       <c r="K355" s="5" t="n">
-        <v>-1.145949</v>
+        <v>0.203225</v>
       </c>
       <c r="L355" s="5" t="n">
-        <v>2.198044</v>
-      </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.146582</v>
+      </c>
+      <c r="M355" s="5" t="n">
+        <v>-0.120286</v>
+      </c>
+      <c r="N355" s="5" t="n">
+        <v>0.395665</v>
       </c>
       <c r="O355" t="inlineStr">
         <is>
@@ -43201,12 +43207,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Other comprehensive earnings (loss)</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Net earnings (loss)</t>
+          <t>Total comprehensive earnings</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
@@ -43230,27 +43236,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I356" s="5" t="n">
-        <v>-0.829992</v>
-      </c>
-      <c r="J356" s="5" t="n">
-        <v>0.717625</v>
-      </c>
-      <c r="K356" s="5" t="n">
-        <v>-1.72221</v>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L356" s="5" t="n">
-        <v>1.688851</v>
-      </c>
-      <c r="M356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.835433</v>
+      </c>
+      <c r="M356" s="5" t="n">
+        <v>0.426989</v>
+      </c>
+      <c r="N356" s="5" t="n">
+        <v>1.925781</v>
       </c>
       <c r="O356" t="inlineStr">
         <is>
@@ -43296,19 +43304,15 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>7.  Finance costs</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Earnings (loss) per share, basic 9 $</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Short term interest</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -43329,27 +43333,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I357" s="5" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="J357" s="5" t="n">
-        <v>5.999999999999999e-08</v>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K357" s="5" t="n">
-        <v>-1.3e-07</v>
+        <v>0.007820000000000001</v>
       </c>
       <c r="L357" s="5" t="n">
-        <v>1.3e-07</v>
-      </c>
-      <c r="M357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00188</v>
+      </c>
+      <c r="M357" s="5" t="n">
+        <v>-0.010292</v>
+      </c>
+      <c r="N357" s="5" t="n">
+        <v>-0.001576</v>
       </c>
       <c r="O357" t="inlineStr">
         <is>
@@ -43395,19 +43399,15 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>7.  Finance costs</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Earnings (loss) per share, diluted 9 $</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Long-term debt interest</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -43428,22 +43428,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I358" s="5" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="J358" s="5" t="n">
-        <v>3e-08</v>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K358" s="5" t="n">
-        <v>-1.3e-07</v>
+        <v>0.568441</v>
       </c>
       <c r="L358" s="5" t="n">
-        <v>5.999999999999999e-08</v>
-      </c>
-      <c r="M358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.507313</v>
+      </c>
+      <c r="M358" s="5" t="n">
+        <v>0.287942</v>
       </c>
       <c r="N358" t="inlineStr">
         <is>
@@ -43494,12 +43496,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Other comprehensive earnings (loss)</t>
+          <t>7.  Finance costs</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Total comprehensive earnings (loss)</t>
+          <t>7.  Finance costs total</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -43523,27 +43525,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I359" s="5" t="n">
-        <v>-0.88509</v>
-      </c>
-      <c r="J359" s="5" t="n">
-        <v>0.79259</v>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>-1.518985</v>
+        <v>0.576261</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>1.835433</v>
-      </c>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.509193</v>
+      </c>
+      <c r="M359" s="5" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="N359" s="5" t="n">
+        <v>-0.001576</v>
       </c>
       <c r="O359" t="inlineStr">
         <is>
@@ -43589,15 +43591,19 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Page | 2</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Net earnings (loss)</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr"/>
+          <t>Other income 6</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -43608,34 +43614,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G360" s="5" t="n">
+        <v>-1.079618</v>
+      </c>
+      <c r="H360" s="5" t="n">
+        <v>-0.799905</v>
       </c>
       <c r="I360" s="5" t="n">
-        <v>-0.829992</v>
+        <v>-0.276387</v>
       </c>
       <c r="J360" s="5" t="n">
-        <v>0.717625</v>
+        <v>-0.067075</v>
       </c>
       <c r="K360" s="5" t="n">
-        <v>-1.72221</v>
-      </c>
-      <c r="L360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.414262</v>
+      </c>
+      <c r="L360" s="5" t="n">
+        <v>-0.352202</v>
+      </c>
+      <c r="M360" s="5" t="n">
+        <v>-0.357047</v>
       </c>
       <c r="N360" t="inlineStr">
         <is>
@@ -43686,15 +43684,19 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>7.    Finance costs</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Short term interest</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr"/>
+          <t>Earnings (loss) from operations</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -43705,25 +43707,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G361" s="5" t="n">
-        <v>0.390055</v>
-      </c>
-      <c r="H361" s="5" t="n">
-        <v>0.261985</v>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I361" s="5" t="n">
-        <v>0.033903</v>
+        <v>-0.372598</v>
       </c>
       <c r="J361" s="5" t="n">
-        <v>0.028503</v>
+        <v>1.304614</v>
       </c>
       <c r="K361" s="5" t="n">
-        <v>0.007820000000000001</v>
-      </c>
-      <c r="L361" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.145949</v>
+      </c>
+      <c r="L361" s="5" t="n">
+        <v>2.198044</v>
       </c>
       <c r="M361" t="inlineStr">
         <is>
@@ -43779,15 +43783,19 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>7.    Finance costs</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Long-term debt interest</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr"/>
+          <t>Net earnings (loss)</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -43809,18 +43817,16 @@
         </is>
       </c>
       <c r="I362" s="5" t="n">
-        <v>0.423491</v>
+        <v>-0.829992</v>
       </c>
       <c r="J362" s="5" t="n">
-        <v>0.558486</v>
+        <v>0.717625</v>
       </c>
       <c r="K362" s="5" t="n">
-        <v>0.568441</v>
-      </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.72221</v>
+      </c>
+      <c r="L362" s="5" t="n">
+        <v>1.688851</v>
       </c>
       <c r="M362" t="inlineStr">
         <is>
@@ -43876,15 +43882,19 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>7.    Finance costs</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>7.    Finance costs total</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr"/>
+          <t>Earnings (loss) per share, basic 9 $</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -43895,25 +43905,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G363" s="5" t="n">
-        <v>0.724956</v>
-      </c>
-      <c r="H363" s="5" t="n">
-        <v>0.345549</v>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I363" s="5" t="n">
-        <v>0.457394</v>
+        <v>-7e-08</v>
       </c>
       <c r="J363" s="5" t="n">
-        <v>0.586989</v>
+        <v>5.999999999999999e-08</v>
       </c>
       <c r="K363" s="5" t="n">
-        <v>0.576261</v>
-      </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.3e-07</v>
+      </c>
+      <c r="L363" s="5" t="n">
+        <v>1.3e-07</v>
       </c>
       <c r="M363" t="inlineStr">
         <is>
@@ -43967,15 +43979,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr"/>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Cost of goods sold 12,23</t>
+          <t>Earnings (loss) per share, diluted 9 $</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -43999,20 +44015,16 @@
         </is>
       </c>
       <c r="I364" s="5" t="n">
-        <v>11.922949</v>
+        <v>-7e-08</v>
       </c>
       <c r="J364" s="5" t="n">
-        <v>13.729972</v>
-      </c>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-08</v>
+      </c>
+      <c r="K364" s="5" t="n">
+        <v>-1.3e-07</v>
+      </c>
+      <c r="L364" s="5" t="n">
+        <v>5.999999999999999e-08</v>
       </c>
       <c r="M364" t="inlineStr">
         <is>
@@ -44068,19 +44080,15 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Other comprehensive earnings (loss)</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Research and development 23</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
+          <t>Total comprehensive earnings (loss)</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -44102,20 +44110,16 @@
         </is>
       </c>
       <c r="I365" s="5" t="n">
-        <v>0.802556</v>
+        <v>-0.88509</v>
       </c>
       <c r="J365" s="5" t="n">
-        <v>0.586561</v>
-      </c>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.79259</v>
+      </c>
+      <c r="K365" s="5" t="n">
+        <v>-1.518985</v>
+      </c>
+      <c r="L365" s="5" t="n">
+        <v>1.835433</v>
       </c>
       <c r="M365" t="inlineStr">
         <is>
@@ -44171,17 +44175,17 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Page | 2</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>General and administration 23</t>
+          <t>Net earnings (loss)</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -44205,15 +44209,13 @@
         </is>
       </c>
       <c r="I366" s="5" t="n">
-        <v>1.739684</v>
+        <v>-0.829992</v>
       </c>
       <c r="J366" s="5" t="n">
-        <v>2.196472</v>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.717625</v>
+      </c>
+      <c r="K366" s="5" t="n">
+        <v>-1.72221</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -44274,19 +44276,15 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>7.    Finance costs</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Research and development 6</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
+          <t>Short term interest</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -44298,23 +44296,19 @@
         </is>
       </c>
       <c r="G367" s="5" t="n">
-        <v>1.892251</v>
+        <v>0.390055</v>
       </c>
       <c r="H367" s="5" t="n">
-        <v>1.071652</v>
+        <v>0.261985</v>
       </c>
       <c r="I367" s="5" t="n">
-        <v>0.770556</v>
-      </c>
-      <c r="J367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.033903</v>
+      </c>
+      <c r="J367" s="5" t="n">
+        <v>0.028503</v>
+      </c>
+      <c r="K367" s="5" t="n">
+        <v>0.007820000000000001</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -44375,19 +44369,15 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>7.    Finance costs</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Long-term debt interest</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -44403,21 +44393,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H368" s="5" t="n">
-        <v>-2.866808</v>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I368" s="5" t="n">
-        <v>-0.372598</v>
-      </c>
-      <c r="J368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.423491</v>
+      </c>
+      <c r="J368" s="5" t="n">
+        <v>0.558486</v>
+      </c>
+      <c r="K368" s="5" t="n">
+        <v>0.568441</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -44478,12 +44466,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>7.    Finance costs</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Loss on remeasurement of debenture 17</t>
+          <t>7.    Finance costs total</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -44497,28 +44485,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G369" s="5" t="n">
+        <v>0.724956</v>
       </c>
       <c r="H369" s="5" t="n">
-        <v>0.157059</v>
-      </c>
-      <c r="I369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.345549</v>
+      </c>
+      <c r="I369" s="5" t="n">
+        <v>0.457394</v>
+      </c>
+      <c r="J369" s="5" t="n">
+        <v>0.586989</v>
+      </c>
+      <c r="K369" s="5" t="n">
+        <v>0.576261</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -44577,17 +44557,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>Expenses (income)</t>
-        </is>
-      </c>
+      <c r="B370" t="inlineStr"/>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Total finance costs</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr"/>
+          <t>Cost of goods sold 12,23</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -44603,16 +44583,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H370" s="5" t="n">
-        <v>0.5026080000000001</v>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I370" s="5" t="n">
-        <v>0.457394</v>
-      </c>
-      <c r="J370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.922949</v>
+      </c>
+      <c r="J370" s="5" t="n">
+        <v>13.729972</v>
       </c>
       <c r="K370" t="inlineStr">
         <is>
@@ -44683,12 +44663,12 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Research and development 23</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -44706,16 +44686,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H371" s="5" t="n">
-        <v>-3.369416</v>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I371" s="5" t="n">
-        <v>-0.829992</v>
-      </c>
-      <c r="J371" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.802556</v>
+      </c>
+      <c r="J371" s="5" t="n">
+        <v>0.586561</v>
       </c>
       <c r="K371" t="inlineStr">
         <is>
@@ -44786,12 +44766,12 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted 9 $</t>
+          <t>General and administration 23</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -44809,16 +44789,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H372" s="5" t="n">
-        <v>-2.8e-07</v>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I372" s="5" t="n">
-        <v>-7e-08</v>
-      </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.739684</v>
+      </c>
+      <c r="J372" s="5" t="n">
+        <v>2.196472</v>
       </c>
       <c r="K372" t="inlineStr">
         <is>
@@ -44884,15 +44864,19 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>7.    Finance costs</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Accretion of deferred financing costs and long-term debt</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr"/>
+          <t>Research and development 6</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -44903,16 +44887,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G373" s="5" t="n">
+        <v>1.892251</v>
       </c>
       <c r="H373" s="5" t="n">
-        <v>0.083564</v>
+        <v>1.071652</v>
       </c>
       <c r="I373" s="5" t="n">
-        <v>0.09335400000000001</v>
+        <v>0.770556</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
@@ -44983,15 +44965,19 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>7.    Finance costs</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Long term interest</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr"/>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -45007,13 +44993,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H374" s="5" t="n">
+        <v>-2.866808</v>
       </c>
       <c r="I374" s="5" t="n">
-        <v>0.330137</v>
+        <v>-0.372598</v>
       </c>
       <c r="J374" t="inlineStr">
         <is>
@@ -45082,28 +45066,34 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr"/>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Cost of goods sold</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E375" s="5" t="n">
-        <v>8.631394</v>
-      </c>
-      <c r="F375" s="5" t="n">
-        <v>11.290303</v>
-      </c>
-      <c r="G375" s="5" t="n">
-        <v>12.315704</v>
+          <t>Loss on remeasurement of debenture 17</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H375" s="5" t="n">
-        <v>9.175905999999999</v>
+        <v>0.157059</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -45184,7 +45174,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Results from operating activities</t>
+          <t>Total finance costs</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -45198,16 +45188,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G376" s="5" t="n">
-        <v>-2.087895</v>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H376" s="5" t="n">
-        <v>-2.866808</v>
-      </c>
-      <c r="I376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5026080000000001</v>
+      </c>
+      <c r="I376" s="5" t="n">
+        <v>0.457394</v>
       </c>
       <c r="J376" t="inlineStr">
         <is>
@@ -45278,17 +45268,17 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Finance and other costs</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Interest expense 7</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -45301,16 +45291,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G377" s="5" t="n">
-        <v>0.390055</v>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H377" s="5" t="n">
-        <v>0.261985</v>
-      </c>
-      <c r="I377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.369416</v>
+      </c>
+      <c r="I377" s="5" t="n">
+        <v>-0.829992</v>
       </c>
       <c r="J377" t="inlineStr">
         <is>
@@ -45381,15 +45371,19 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Finance and other costs</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Accretion of finance and warrant costs 7</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr"/>
+          <t>Loss per share, basic and diluted 9 $</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -45400,16 +45394,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G378" s="5" t="n">
-        <v>0.334901</v>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H378" s="5" t="n">
-        <v>0.083564</v>
-      </c>
-      <c r="I378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.8e-07</v>
+      </c>
+      <c r="I378" s="5" t="n">
+        <v>-7e-08</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
@@ -45480,12 +45474,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Finance and other costs</t>
+          <t>7.    Finance costs</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Loss on remeasurement of debenture 7,16</t>
+          <t>Accretion of deferred financing costs and long-term debt</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -45505,12 +45499,10 @@
         </is>
       </c>
       <c r="H379" s="5" t="n">
-        <v>0.157059</v>
-      </c>
-      <c r="I379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.083564</v>
+      </c>
+      <c r="I379" s="5" t="n">
+        <v>0.09335400000000001</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
@@ -45581,12 +45573,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Finance and other costs</t>
+          <t>7.    Finance costs</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Write down of long-term tax asset</t>
+          <t>Long term interest</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -45600,18 +45592,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G380" s="5" t="n">
-        <v>0.25</v>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I380" s="5" t="n">
+        <v>0.330137</v>
       </c>
       <c r="J380" t="inlineStr">
         <is>
@@ -45680,32 +45672,28 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>Finance and other costs</t>
-        </is>
-      </c>
+      <c r="B381" t="inlineStr"/>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Total finance and other costs</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cost of goods sold</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E381" s="5" t="n">
+        <v>8.631394</v>
+      </c>
+      <c r="F381" s="5" t="n">
+        <v>11.290303</v>
       </c>
       <c r="G381" s="5" t="n">
-        <v>0.724956</v>
+        <v>12.315704</v>
       </c>
       <c r="H381" s="5" t="n">
-        <v>0.5026080000000001</v>
+        <v>9.175905999999999</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
@@ -45781,19 +45769,15 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Finance and other costs</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Results from operating activities</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -45805,10 +45789,10 @@
         </is>
       </c>
       <c r="G382" s="5" t="n">
-        <v>-2.812851</v>
+        <v>-2.087895</v>
       </c>
       <c r="H382" s="5" t="n">
-        <v>-3.369416</v>
+        <v>-2.866808</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
@@ -45889,12 +45873,12 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Loss per share basic and diluted 9 $</t>
+          <t>Interest expense 7</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -45908,10 +45892,10 @@
         </is>
       </c>
       <c r="G383" s="5" t="n">
-        <v>-2.6e-07</v>
+        <v>0.390055</v>
       </c>
       <c r="H383" s="5" t="n">
-        <v>-2.8e-07</v>
+        <v>0.261985</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
@@ -45987,12 +45971,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>7.    Finance costs</t>
+          <t>Finance and other costs</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Accretion of financing and warrant costs</t>
+          <t>Accretion of finance and warrant costs 7</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -46086,12 +46070,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>7.    Finance costs</t>
+          <t>Finance and other costs</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Loss on remeasurement of debenture</t>
+          <t>Loss on remeasurement of debenture 7,16</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -46185,27 +46169,29 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr"/>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Finance and other costs</t>
+        </is>
+      </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Revenue $</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E386" s="5" t="n">
-        <v>14.400071</v>
-      </c>
-      <c r="F386" s="5" t="n">
-        <v>18.878218</v>
-      </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Write down of long-term tax asset</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G386" s="5" t="n">
+        <v>0.25</v>
       </c>
       <c r="H386" t="inlineStr">
         <is>
@@ -46286,34 +46272,30 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Finance and other costs</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Research and development (note 11)</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopment</t>
-        </is>
-      </c>
-      <c r="E387" s="5" t="n">
-        <v>1.032714</v>
-      </c>
-      <c r="F387" s="5" t="n">
-        <v>1.19154</v>
-      </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total finance and other costs</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G387" s="5" t="n">
+        <v>0.724956</v>
+      </c>
+      <c r="H387" s="5" t="n">
+        <v>0.5026080000000001</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
@@ -46389,30 +46371,34 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Finance and other costs</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Government assistance (note 11)</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
-      <c r="E388" s="5" t="n">
-        <v>-0.458262</v>
-      </c>
-      <c r="F388" s="5" t="n">
-        <v>-0.995397</v>
-      </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G388" s="5" t="n">
+        <v>-2.812851</v>
+      </c>
+      <c r="H388" s="5" t="n">
+        <v>-3.369416</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
@@ -46488,30 +46474,34 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>Finance and other costs</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Stock option compensation (note 10)</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
-      <c r="E389" s="5" t="n">
-        <v>0.279724</v>
-      </c>
-      <c r="F389" s="5" t="n">
-        <v>0.231202</v>
-      </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss per share basic and diluted 9 $</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G389" s="5" t="n">
+        <v>-2.6e-07</v>
+      </c>
+      <c r="H389" s="5" t="n">
+        <v>-2.8e-07</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
@@ -46587,30 +46577,30 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>7.    Finance costs</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Earnings (loss) before the following</t>
+          <t>Accretion of financing and warrant costs</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
-      <c r="E390" s="5" t="n">
-        <v>-0.287087</v>
-      </c>
-      <c r="F390" s="5" t="n">
-        <v>1.386593</v>
-      </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G390" s="5" t="n">
+        <v>0.334901</v>
+      </c>
+      <c r="H390" s="5" t="n">
+        <v>0.083564</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -46686,30 +46676,32 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Expenses (income)</t>
+          <t>7.    Finance costs</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Amortization of plant and equipment</t>
+          <t>Loss on remeasurement of debenture</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
-      <c r="E391" s="5" t="n">
-        <v>0.297096</v>
-      </c>
-      <c r="F391" s="5" t="n">
-        <v>0.218121</v>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H391" s="5" t="n">
+        <v>0.157059</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
@@ -46783,27 +46775,25 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>Expenses (income)</t>
-        </is>
-      </c>
+      <c r="B392" t="inlineStr"/>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Amortization of technology, patents and other assets</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr"/>
+          <t>Revenue $</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E392" s="5" t="n">
-        <v>0.246593</v>
+        <v>14.400071</v>
       </c>
       <c r="F392" s="5" t="n">
-        <v>0.258218</v>
-      </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18.878218</v>
+      </c>
+      <c r="G392" s="5" t="n">
+        <v>17.359556</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
@@ -46889,20 +46879,24 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Accretion of deferred financing costs</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr"/>
-      <c r="E393" s="5" t="n">
-        <v>0.013816</v>
+          <t>Research and development (note 10)</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F393" s="5" t="n">
-        <v>0.091768</v>
-      </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.19154</v>
+      </c>
+      <c r="G393" s="5" t="n">
+        <v>1.758772</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
@@ -46988,20 +46982,20 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Accretion of warrant costs</t>
+          <t>Government assistance (note 10)</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
-      <c r="E394" s="5" t="n">
-        <v>0.017787</v>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F394" s="5" t="n">
-        <v>0.119268</v>
-      </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.995397</v>
+      </c>
+      <c r="G394" s="5" t="n">
+        <v>-1.133609</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
@@ -47087,24 +47081,20 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Loss (gain) on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
-      <c r="E395" s="5" t="n">
-        <v>-0.506769</v>
+          <t>Stock option compensation (note 9)</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F395" s="5" t="n">
-        <v>0.808829</v>
-      </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.231202</v>
+      </c>
+      <c r="G395" s="5" t="n">
+        <v>0.181922</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
@@ -47190,20 +47180,18 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Interest - short -term</t>
+          <t>Earnings (loss) before the following</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
       <c r="E396" s="5" t="n">
-        <v>0.010168</v>
+        <v>-0.287087</v>
       </c>
       <c r="F396" s="5" t="n">
-        <v>0.010727</v>
-      </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.386593</v>
+      </c>
+      <c r="G396" s="5" t="n">
+        <v>-1.544083</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
@@ -47289,20 +47277,18 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Interest - long-term</t>
+          <t>Amortization of plant and equipment</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
       <c r="E397" s="5" t="n">
-        <v>0.06375</v>
+        <v>0.297096</v>
       </c>
       <c r="F397" s="5" t="n">
-        <v>0.3825</v>
-      </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.218121</v>
+      </c>
+      <c r="G397" s="5" t="n">
+        <v>0.333272</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
@@ -47388,20 +47374,18 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Total other expenses</t>
+          <t>Amortization of technology, patents and other assets</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
       <c r="E398" s="5" t="n">
-        <v>0.142441</v>
+        <v>0.246593</v>
       </c>
       <c r="F398" s="5" t="n">
-        <v>1.889431</v>
-      </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.258218</v>
+      </c>
+      <c r="G398" s="5" t="n">
+        <v>0.25241</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
@@ -47487,24 +47471,18 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Accretion of deferred financing costs</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
       <c r="E399" s="5" t="n">
-        <v>-0.429528</v>
+        <v>0.013816</v>
       </c>
       <c r="F399" s="5" t="n">
-        <v>-0.502838</v>
-      </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.091768</v>
+      </c>
+      <c r="G399" s="5" t="n">
+        <v>0.143468</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
@@ -47590,26 +47568,18 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Current income tax expense (note 8)</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Accretion of warrant costs</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr"/>
       <c r="E400" s="5" t="n">
-        <v>0.002708</v>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.017787</v>
+      </c>
+      <c r="F400" s="5" t="n">
+        <v>0.119268</v>
+      </c>
+      <c r="G400" s="5" t="n">
+        <v>0.191433</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
@@ -47695,24 +47665,22 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
+          <t>Loss (gain) on foreign exchange</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ForeignExchangeTradingGains</t>
         </is>
       </c>
       <c r="E401" s="5" t="n">
-        <v>-0.432236</v>
+        <v>-0.506769</v>
       </c>
       <c r="F401" s="5" t="n">
-        <v>-0.502838</v>
-      </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.808829</v>
+      </c>
+      <c r="G401" s="5" t="n">
+        <v>0.03306</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
@@ -47793,29 +47761,27 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Earnings per share</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Basic $</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E402" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="F402" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Write down of long term tax asset (note 7)</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G402" s="5" t="n">
+        <v>0.25</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
@@ -47896,29 +47862,23 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Earnings per share</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Diluted</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Interest - short -term</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
       <c r="E403" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.010168</v>
       </c>
       <c r="F403" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010727</v>
+      </c>
+      <c r="G403" s="5" t="n">
+        <v>0.007555</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
@@ -47999,25 +47959,23 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Capital      Surplus           Deficit           Total</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Balance as at January 1, 2008 $ 13,171,212 $ 506,218 $</t>
+          <t>Interest - long-term</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
       <c r="E404" s="5" t="n">
-        <v>8.518503000000001</v>
+        <v>0.06375</v>
       </c>
       <c r="F404" s="5" t="n">
-        <v>-5.158927</v>
-      </c>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3825</v>
+      </c>
+      <c r="G404" s="5" t="n">
+        <v>0.3825</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
@@ -48098,25 +48056,23 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Capital      Surplus           Deficit           Total</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Loss for the year ended December 31, 2008 - -</t>
+          <t>Total other expenses</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
       <c r="E405" s="5" t="n">
-        <v>-0.432236</v>
+        <v>0.142441</v>
       </c>
       <c r="F405" s="5" t="n">
-        <v>-0.432236</v>
-      </c>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.889431</v>
+      </c>
+      <c r="G405" s="5" t="n">
+        <v>1.593698</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
@@ -48197,27 +48153,27 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Capital      Surplus           Deficit           Total</t>
+          <t>Expenses (income)</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Stock option compensation - 279,724</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr"/>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E406" s="5" t="n">
-        <v>0.279724</v>
-      </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.432236</v>
+      </c>
+      <c r="F406" s="5" t="n">
+        <v>-0.502838</v>
+      </c>
+      <c r="G406" s="5" t="n">
+        <v>-3.137781</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
@@ -48298,27 +48254,27 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Capital      Surplus           Deficit           Total</t>
+          <t>Earnings per share</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Warrants issued - 423,461</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr"/>
+          <t>Basic $</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E407" s="5" t="n">
-        <v>0.423461</v>
-      </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="F407" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="G407" s="5" t="n">
+        <v>-2.6e-07</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
@@ -48399,25 +48355,27 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Capital      Surplus           Deficit           Total</t>
+          <t>Earnings per share</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Balance as at December 31, 2008 13,171,212 1,209,403</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E408" s="5" t="n">
-        <v>8.789452000000001</v>
+        <v>-4e-08</v>
       </c>
       <c r="F408" s="5" t="n">
-        <v>-5.591163</v>
-      </c>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="G408" s="5" t="n">
+        <v>-2.6e-07</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
@@ -48503,20 +48461,20 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Loss for the year ended December 31, 2009 - -</t>
+          <t>Balance as at January 1, 2009 $ 13,171,212 $ 1,209,403 $</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
-      <c r="E409" s="5" t="n">
-        <v>-0.502838</v>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F409" s="5" t="n">
-        <v>-0.502838</v>
-      </c>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.789452000000001</v>
+      </c>
+      <c r="G409" s="5" t="n">
+        <v>-5.591163</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
@@ -48602,22 +48560,18 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Stock option compensation (note 10) - 231,202</t>
+          <t>Loss for the year ended December 31, 2009 - -</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
       <c r="E410" s="5" t="n">
-        <v>0.231202</v>
-      </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.502838</v>
+      </c>
+      <c r="F410" s="5" t="n">
+        <v>-0.502838</v>
+      </c>
+      <c r="G410" s="5" t="n">
+        <v>-0.502838</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
@@ -48703,17 +48657,17 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Issuance of common shares (note 9) 30,000 -</t>
+          <t>Stock option compensation - 231,202</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
-      <c r="E411" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F411" s="5" t="n">
+        <v>0.231202</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
@@ -48804,87 +48758,1796 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
+          <t>Common shares issued 30,000 -</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F412" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Balance as at December 31, 2009 13,201,212 1,440,605</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F413" s="5" t="n">
+        <v>8.547815999999999</v>
+      </c>
+      <c r="G413" s="5" t="n">
+        <v>-6.094001</v>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Loss for the year ended December 31, 2010 - -</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F414" s="5" t="n">
+        <v>-3.137781</v>
+      </c>
+      <c r="G414" s="5" t="n">
+        <v>-3.137781</v>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Stock option compensation (note 9) - 181,922</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F415" s="5" t="n">
+        <v>0.181922</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Balance as at December 31, 2010 $ 13,201,212 $ 1,622,527 $</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F416" s="5" t="n">
+        <v>5.591957</v>
+      </c>
+      <c r="G416" s="5" t="n">
+        <v>-9.231782000000001</v>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Research and development (note 11)</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
+      <c r="E417" s="5" t="n">
+        <v>1.032714</v>
+      </c>
+      <c r="F417" s="5" t="n">
+        <v>1.19154</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Government assistance (note 11)</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" s="5" t="n">
+        <v>-0.458262</v>
+      </c>
+      <c r="F418" s="5" t="n">
+        <v>-0.995397</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Stock option compensation (note 10)</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" s="5" t="n">
+        <v>0.279724</v>
+      </c>
+      <c r="F419" s="5" t="n">
+        <v>0.231202</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E420" s="5" t="n">
+        <v>-0.429528</v>
+      </c>
+      <c r="F420" s="5" t="n">
+        <v>-0.502838</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Expenses (income)</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Current income tax expense (note 8)</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E421" s="5" t="n">
+        <v>0.002708</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Balance as at January 1, 2008 $ 13,171,212 $ 506,218 $</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" s="5" t="n">
+        <v>8.518503000000001</v>
+      </c>
+      <c r="F422" s="5" t="n">
+        <v>-5.158927</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Loss for the year ended December 31, 2008 - -</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" s="5" t="n">
+        <v>-0.432236</v>
+      </c>
+      <c r="F423" s="5" t="n">
+        <v>-0.432236</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Stock option compensation - 279,724</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" s="5" t="n">
+        <v>0.279724</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Warrants issued - 423,461</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" s="5" t="n">
+        <v>0.423461</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Balance as at December 31, 2008 13,171,212 1,209,403</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" s="5" t="n">
+        <v>8.789452000000001</v>
+      </c>
+      <c r="F426" s="5" t="n">
+        <v>-5.591163</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Stock option compensation (note 10) - 231,202</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" s="5" t="n">
+        <v>0.231202</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Issuance of common shares (note 9) 30,000 -</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Capital      Surplus           Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
           <t>Balance as at December 31, 2009 $ 13,201,212 $ 1,440,605 $</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" s="5" t="n">
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" s="5" t="n">
         <v>8.547815999999999</v>
       </c>
-      <c r="F412" s="5" t="n">
+      <c r="F429" s="5" t="n">
         <v>-6.094001</v>
       </c>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U412" t="inlineStr">
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
         <is>
           <t>-</t>
         </is>
